--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N84_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N84_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>11.89566338474689</v>
+        <v>1.933045300021369</v>
       </c>
       <c r="D2" t="n">
-        <v>10.70317809191817</v>
+        <v>1.739266439936703</v>
       </c>
       <c r="E2" t="n">
-        <v>14.09621867215382</v>
+        <v>2.290635534224996</v>
       </c>
       <c r="F2" t="n">
-        <v>12.03279889302884</v>
+        <v>1.955329820117187</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>9.646781134204362</v>
+        <v>1.567601934308209</v>
       </c>
       <c r="D3" t="n">
-        <v>10.84066640074103</v>
+        <v>1.761608290120417</v>
       </c>
       <c r="E3" t="n">
-        <v>14.09621867215382</v>
+        <v>2.290635534224996</v>
       </c>
       <c r="F3" t="n">
-        <v>12.03279889302884</v>
+        <v>1.955329820117187</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.73116487875869</v>
+        <v>5.968814292798287</v>
       </c>
       <c r="D4" t="n">
-        <v>35.53371040992055</v>
+        <v>5.77422794161209</v>
       </c>
       <c r="E4" t="n">
-        <v>14.09621867215382</v>
+        <v>2.290635534224996</v>
       </c>
       <c r="F4" t="n">
-        <v>12.03279889302884</v>
+        <v>1.955329820117187</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.44057676194621</v>
+        <v>6.40909372381626</v>
       </c>
       <c r="D5" t="n">
-        <v>40.13932511872336</v>
+        <v>6.522640331792545</v>
       </c>
       <c r="E5" t="n">
-        <v>14.09621867215382</v>
+        <v>2.290635534224996</v>
       </c>
       <c r="F5" t="n">
-        <v>12.03279889302884</v>
+        <v>1.955329820117187</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>36.46151170857075</v>
+        <v>5.924995652642748</v>
       </c>
       <c r="D6" t="n">
-        <v>36.31553607443779</v>
+        <v>5.901274612096142</v>
       </c>
       <c r="E6" t="n">
-        <v>14.09621867215382</v>
+        <v>2.290635534224996</v>
       </c>
       <c r="F6" t="n">
-        <v>12.03279889302884</v>
+        <v>1.955329820117187</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>44.16188138355435</v>
+        <v>7.176305724827582</v>
       </c>
       <c r="D7" t="n">
-        <v>43.56373794063964</v>
+        <v>7.079107415353942</v>
       </c>
       <c r="E7" t="n">
-        <v>14.09621867215382</v>
+        <v>2.290635534224996</v>
       </c>
       <c r="F7" t="n">
-        <v>12.03279889302884</v>
+        <v>1.955329820117187</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>39.45275448285031</v>
+        <v>6.411072603463175</v>
       </c>
       <c r="D8" t="n">
-        <v>39.08500764778537</v>
+        <v>6.351313742765123</v>
       </c>
       <c r="E8" t="n">
-        <v>14.09621867215382</v>
+        <v>2.290635534224996</v>
       </c>
       <c r="F8" t="n">
-        <v>12.03279889302884</v>
+        <v>1.955329820117187</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>18.82362112779295</v>
+        <v>3.058838433266354</v>
       </c>
       <c r="D9" t="n">
-        <v>34.7986052496469</v>
+        <v>5.654773353067622</v>
       </c>
       <c r="E9" t="n">
-        <v>14.09621867215382</v>
+        <v>2.290635534224996</v>
       </c>
       <c r="F9" t="n">
-        <v>12.03279889302884</v>
+        <v>1.955329820117187</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>6.909020304166074</v>
+        <v>1.122715799426987</v>
       </c>
       <c r="D10" t="n">
-        <v>19.95553791155904</v>
+        <v>3.242774910628344</v>
       </c>
       <c r="E10" t="n">
-        <v>14.09621867215382</v>
+        <v>2.290635534224996</v>
       </c>
       <c r="F10" t="n">
-        <v>12.03279889302884</v>
+        <v>1.955329820117187</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
